--- a/ABC Store – Annual Sales & Customer Analytics Dashboard 2025.xlsx
+++ b/ABC Store – Annual Sales & Customer Analytics Dashboard 2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Project excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Main\Desktop\Project excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD13403-06EC-495E-8DD4-758F3F45E660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE54744-4E03-4B13-AC5E-886500B2F5EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="888" activeTab="2" xr2:uid="{11C7DA85-D15C-4321-B4C2-592E74656A4F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="888" activeTab="1" xr2:uid="{11C7DA85-D15C-4321-B4C2-592E74656A4F}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="254">
   <si>
     <t>Index</t>
   </si>
@@ -823,6 +823,9 @@
   <si>
     <t>ABC Store – Annual Sales &amp; Customer Analytics Dashboard 2025</t>
   </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
 </sst>
 </file>
 
@@ -1014,18 +1017,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1043,6 +1034,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1080,7 +1083,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[dashbord3.xlsx]order vs sales!PivotTable1</c:name>
+    <c:name>[ABC Store – Annual Sales &amp; Customer Analytics Dashboard 2025.xlsx]order vs sales!PivotTable1</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -1543,7 +1546,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'order vs sales'!$A$4:$A$15</c:f>
+              <c:f>'order vs sales'!$A$4:$A$16</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -1587,7 +1590,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'order vs sales'!$B$4:$B$15</c:f>
+              <c:f>'order vs sales'!$B$4:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1662,7 +1665,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'order vs sales'!$A$4:$A$15</c:f>
+              <c:f>'order vs sales'!$A$4:$A$16</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -1706,7 +1709,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'order vs sales'!$C$4:$C$15</c:f>
+              <c:f>'order vs sales'!$C$4:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1983,7 +1986,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[dashbord3.xlsx]Top 3 States!PivotTable5</c:name>
+    <c:name>[ABC Store – Annual Sales &amp; Customer Analytics Dashboard 2025.xlsx]Top 3 States!PivotTable5</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -2475,7 +2478,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[dashbord3.xlsx]Age Vs Gender!PivotTable6</c:name>
+    <c:name>[ABC Store – Annual Sales &amp; Customer Analytics Dashboard 2025.xlsx]Age Vs Gender!PivotTable6</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -3216,7 +3219,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[dashbord3.xlsx]channel!PivotTable7</c:name>
+    <c:name>[ABC Store – Annual Sales &amp; Customer Analytics Dashboard 2025.xlsx]channel!PivotTable7</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -3847,7 +3850,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[dashbord3.xlsx]female vs man!PivotTable2</c:name>
+    <c:name>[ABC Store – Annual Sales &amp; Customer Analytics Dashboard 2025.xlsx]female vs man!PivotTable2</c:name>
     <c:fmtId val="2"/>
   </c:pivotSource>
   <c:chart>
@@ -4865,7 +4868,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[dashbord3.xlsx]oder status!PivotTable3</c:name>
+    <c:name>[ABC Store – Annual Sales &amp; Customer Analytics Dashboard 2025.xlsx]oder status!PivotTable3</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -6025,7 +6028,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[dashbord3.xlsx]Top 3 States!PivotTable5</c:name>
+    <c:name>[ABC Store – Annual Sales &amp; Customer Analytics Dashboard 2025.xlsx]Top 3 States!PivotTable5</c:name>
     <c:fmtId val="2"/>
   </c:pivotSource>
   <c:chart>
@@ -6591,7 +6594,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[dashbord3.xlsx]Age Vs Gender!PivotTable6</c:name>
+    <c:name>[ABC Store – Annual Sales &amp; Customer Analytics Dashboard 2025.xlsx]Age Vs Gender!PivotTable6</c:name>
     <c:fmtId val="2"/>
   </c:pivotSource>
   <c:chart>
@@ -7566,7 +7569,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[dashbord3.xlsx]channel!PivotTable7</c:name>
+    <c:name>[ABC Store – Annual Sales &amp; Customer Analytics Dashboard 2025.xlsx]channel!PivotTable7</c:name>
     <c:fmtId val="2"/>
   </c:pivotSource>
   <c:chart>
@@ -8629,7 +8632,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[dashbord3.xlsx]order vs sales!PivotTable1</c:name>
+    <c:name>[ABC Store – Annual Sales &amp; Customer Analytics Dashboard 2025.xlsx]order vs sales!PivotTable1</c:name>
     <c:fmtId val="1"/>
   </c:pivotSource>
   <c:chart>
@@ -8860,7 +8863,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'order vs sales'!$A$4:$A$15</c:f>
+              <c:f>'order vs sales'!$A$4:$A$16</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -8904,7 +8907,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'order vs sales'!$B$4:$B$15</c:f>
+              <c:f>'order vs sales'!$B$4:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -8981,7 +8984,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'order vs sales'!$A$4:$A$15</c:f>
+              <c:f>'order vs sales'!$A$4:$A$16</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -9025,7 +9028,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'order vs sales'!$C$4:$C$15</c:f>
+              <c:f>'order vs sales'!$C$4:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -9302,7 +9305,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[dashbord3.xlsx]female vs man!PivotTable2</c:name>
+    <c:name>[ABC Store – Annual Sales &amp; Customer Analytics Dashboard 2025.xlsx]female vs man!PivotTable2</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -9924,7 +9927,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[dashbord3.xlsx]oder status!PivotTable3</c:name>
+    <c:name>[ABC Store – Annual Sales &amp; Customer Analytics Dashboard 2025.xlsx]oder status!PivotTable3</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -19446,8 +19449,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{22EE371E-B47A-417D-B3A8-973BF5B40676}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="A3:C15" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{22EE371E-B47A-417D-B3A8-973BF5B40676}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="A3:C16" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="22">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -19566,7 +19569,7 @@
   <rowFields count="1">
     <field x="7"/>
   </rowFields>
-  <rowItems count="12">
+  <rowItems count="13">
     <i>
       <x/>
     </i>
@@ -19602,6 +19605,9 @@
     </i>
     <i>
       <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
     </i>
   </rowItems>
   <colFields count="1">
@@ -21268,9 +21274,14 @@
   <dimension ref="A1:V51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="2" max="2" width="12.77734375" customWidth="1"/>
     <col min="7" max="7" width="17.6640625" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" customWidth="1"/>
+    <col min="17" max="17" width="12.77734375" customWidth="1"/>
     <col min="18" max="18" width="16.109375" customWidth="1"/>
     <col min="19" max="19" width="15.109375" customWidth="1"/>
+    <col min="20" max="20" width="11.77734375" customWidth="1"/>
+    <col min="21" max="21" width="10.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
@@ -24857,74 +24868,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="12" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="13" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="13" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="16" t="s">
         <v>238</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="13" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="13" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="13" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="16" t="s">
         <v>247</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="13" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="13" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="14" t="s">
         <v>251</v>
       </c>
     </row>
@@ -24940,94 +24951,94 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="6:30" x14ac:dyDescent="0.3">
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="18" t="s">
         <v>252</v>
       </c>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
-      <c r="U2" s="13"/>
-      <c r="V2" s="13"/>
-      <c r="W2" s="13"/>
-      <c r="X2" s="13"/>
-      <c r="Y2" s="13"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="19"/>
+      <c r="T2" s="19"/>
+      <c r="U2" s="19"/>
+      <c r="V2" s="19"/>
+      <c r="W2" s="19"/>
+      <c r="X2" s="19"/>
+      <c r="Y2" s="19"/>
     </row>
     <row r="3" spans="6:30" x14ac:dyDescent="0.3">
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="13"/>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
+      <c r="T3" s="19"/>
+      <c r="U3" s="19"/>
+      <c r="V3" s="19"/>
+      <c r="W3" s="19"/>
+      <c r="X3" s="19"/>
+      <c r="Y3" s="19"/>
     </row>
     <row r="4" spans="6:30" x14ac:dyDescent="0.3">
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14"/>
-      <c r="T4" s="14"/>
-      <c r="U4" s="14"/>
-      <c r="V4" s="14"/>
-      <c r="W4" s="14"/>
-      <c r="X4" s="14"/>
-      <c r="Y4" s="14"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="20"/>
+      <c r="U4" s="20"/>
+      <c r="V4" s="20"/>
+      <c r="W4" s="20"/>
+      <c r="X4" s="20"/>
+      <c r="Y4" s="20"/>
     </row>
     <row r="5" spans="6:30" x14ac:dyDescent="0.3">
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15"/>
-      <c r="T5" s="15"/>
-      <c r="U5" s="15"/>
-      <c r="V5" s="15"/>
-      <c r="W5" s="15"/>
-      <c r="X5" s="15"/>
-      <c r="Y5" s="15"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="21"/>
+      <c r="N5" s="21"/>
+      <c r="O5" s="21"/>
+      <c r="P5" s="21"/>
+      <c r="Q5" s="21"/>
+      <c r="R5" s="21"/>
+      <c r="S5" s="21"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="21"/>
+      <c r="V5" s="21"/>
+      <c r="W5" s="21"/>
+      <c r="X5" s="21"/>
+      <c r="Y5" s="21"/>
     </row>
     <row r="6" spans="6:30" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="7" spans="6:30" x14ac:dyDescent="0.3">
@@ -25056,7 +25067,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABD8651B-C99E-40CE-8600-90E742A59FA9}">
-  <dimension ref="A3:C15"/>
+  <dimension ref="A3:C16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -25205,6 +25216,17 @@
       </c>
       <c r="C15" s="8">
         <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="B16" s="8">
+        <v>204323</v>
+      </c>
+      <c r="C16" s="8">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
